--- a/data/raw/inventory/Week 34/Audio_Array/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 34/Audio_Array/Seller FBA Inventory (SP-API).xlsx
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F2" t="n">
         <v>104</v>
@@ -535,10 +535,10 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L2" t="n">
         <v>1</v>
@@ -600,10 +600,10 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -644,10 +644,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
         <v>5</v>
@@ -662,7 +662,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -768,25 +768,25 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
         <v>26</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>28</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1391,7 +1391,7 @@
         <v>37</v>
       </c>
       <c r="F16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G16" t="n">
         <v>24</v>
@@ -1403,13 +1403,13 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>1</v>
@@ -1530,10 +1530,10 @@
         <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -2147,10 +2147,10 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F35" t="n">
         <v>37</v>
@@ -2581,10 +2581,10 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -3682,10 +3682,10 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F53" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G53" t="n">
         <v>6</v>
@@ -3700,7 +3700,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -4057,7 +4057,7 @@
         <v>16</v>
       </c>
       <c r="F59" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -4069,7 +4069,7 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K59" t="n">
         <v>16</v>
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F77" t="n">
         <v>30</v>
@@ -5185,10 +5185,10 @@
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L77" t="n">
         <v>1</v>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F97" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G97" t="n">
         <v>15</v>
@@ -6425,10 +6425,10 @@
         <v>1</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K97" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
@@ -7402,10 +7402,10 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F113" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -7420,7 +7420,7 @@
         <v>1</v>
       </c>
       <c r="K113" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L113" t="n">
         <v>1</v>
@@ -7712,10 +7712,10 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F118" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -7730,7 +7730,7 @@
         <v>1</v>
       </c>
       <c r="K118" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L118" t="n">
         <v>1</v>
@@ -8022,10 +8022,10 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F123" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -8040,7 +8040,7 @@
         <v>1</v>
       </c>
       <c r="K123" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L123" t="n">
         <v>0</v>
@@ -8208,7 +8208,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F126" t="n">
         <v>25</v>
@@ -8223,10 +8223,10 @@
         <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L126" t="n">
         <v>1</v>
@@ -8285,7 +8285,7 @@
         <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K127" t="n">
         <v>1</v>
@@ -8294,7 +8294,7 @@
         <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N127" t="inlineStr">
         <is>
@@ -8580,10 +8580,10 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F132" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G132" t="n">
         <v>10</v>
@@ -8598,7 +8598,7 @@
         <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L132" t="n">
         <v>0</v>
@@ -9200,10 +9200,10 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F142" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -9215,10 +9215,10 @@
         <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K142" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L142" t="n">
         <v>0</v>
@@ -9947,7 +9947,7 @@
         <v>34</v>
       </c>
       <c r="F154" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -9959,7 +9959,7 @@
         <v>0</v>
       </c>
       <c r="J154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K154" t="n">
         <v>34</v>
@@ -10192,7 +10192,7 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F158" t="n">
         <v>0</v>
@@ -10207,10 +10207,10 @@
         <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K158" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L158" t="n">
         <v>0</v>
@@ -10316,7 +10316,7 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F160" t="n">
         <v>6</v>
@@ -10331,10 +10331,10 @@
         <v>0</v>
       </c>
       <c r="J160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K160" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L160" t="n">
         <v>1</v>
@@ -11680,10 +11680,10 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="F182" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="G182" t="n">
         <v>200</v>
@@ -11695,10 +11695,10 @@
         <v>24</v>
       </c>
       <c r="J182" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K182" t="n">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="L182" t="n">
         <v>0</v>
@@ -11742,10 +11742,10 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F183" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -11760,7 +11760,7 @@
         <v>1</v>
       </c>
       <c r="K183" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L183" t="n">
         <v>1</v>
@@ -12982,7 +12982,7 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F203" t="n">
         <v>17</v>
@@ -12997,10 +12997,10 @@
         <v>0</v>
       </c>
       <c r="J203" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K203" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="L203" t="n">
         <v>0</v>

--- a/data/raw/inventory/Week 34/Audio_Array/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 34/Audio_Array/Seller FBA Inventory (SP-API).xlsx
@@ -1530,10 +1530,10 @@
         <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -4488,7 +4488,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F66" t="n">
         <v>6</v>
@@ -4503,10 +4503,10 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K66" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -5728,10 +5728,10 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F86" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -5746,7 +5746,7 @@
         <v>8</v>
       </c>
       <c r="K86" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
@@ -6413,7 +6413,7 @@
         <v>46</v>
       </c>
       <c r="F97" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G97" t="n">
         <v>15</v>
@@ -6425,7 +6425,7 @@
         <v>1</v>
       </c>
       <c r="J97" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K97" t="n">
         <v>46</v>
@@ -7963,7 +7963,7 @@
         <v>36</v>
       </c>
       <c r="F122" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -7975,7 +7975,7 @@
         <v>0</v>
       </c>
       <c r="J122" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K122" t="n">
         <v>36</v>
@@ -10192,10 +10192,10 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F158" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G158" t="n">
         <v>20</v>
@@ -10210,7 +10210,7 @@
         <v>3</v>
       </c>
       <c r="K158" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L158" t="n">
         <v>0</v>
@@ -12132,10 +12132,10 @@
         <v>0</v>
       </c>
       <c r="K189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M189" t="n">
         <v>0</v>
